--- a/pages/CdA Testing/Track CdA Testing.xlsx
+++ b/pages/CdA Testing/Track CdA Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88AD16C-6042-4261-8F03-9B4B83146A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE58AF33-2CC4-4EBC-BC47-A4D43A1705DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/pages/CdA Testing/Track CdA Testing.xlsx
+++ b/pages/CdA Testing/Track CdA Testing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SamB\CNZPD\pages\CdA Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE58AF33-2CC4-4EBC-BC47-A4D43A1705DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9FEBC2-BE11-4039-8412-CA3B51815F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3061" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3109" uniqueCount="417">
   <si>
     <t>Squad</t>
   </si>
@@ -1312,6 +1312,33 @@
   </si>
   <si>
     <t>https://youtu.be/6wyZ_ILel4o</t>
+  </si>
+  <si>
+    <t>Prue Fowler</t>
+  </si>
+  <si>
+    <t>Baseline testing - working on 'flat back'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Col - long sleeve </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nil </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avanti TP M </t>
+  </si>
+  <si>
+    <t>https://youtu.be/M3zJwcWeUnY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/U6dWIim4nfY</t>
+  </si>
+  <si>
+    <t>https://youtu.be/Wv3emYB08bk</t>
+  </si>
+  <si>
+    <t>https://youtu.be/ymB6fodompM</t>
   </si>
 </sst>
 </file>
@@ -1529,7 +1556,7 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1775,10 +1802,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1811,80 +1838,53 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2702,8 +2702,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:AH309" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
-  <autoFilter ref="A1:AH309" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Track_TT23" displayName="Track_TT23" ref="A1:AH313" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+  <autoFilter ref="A1:AH313" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH309">
     <sortCondition ref="A1:A309"/>
   </sortState>
@@ -3010,7 +3010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:AH309"/>
+  <dimension ref="A1:AH313"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5546875" style="2" customWidth="1"/>
@@ -4220,9 +4220,9 @@
       <c r="AD14" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="AE14" s="107"/>
-      <c r="AF14" s="107"/>
-      <c r="AG14" s="109">
+      <c r="AE14" s="97"/>
+      <c r="AF14" s="97"/>
+      <c r="AG14" s="99">
         <v>1.1739999999999999</v>
       </c>
       <c r="AH14" s="3">
@@ -4868,37 +4868,35 @@
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A23" s="95" t="s">
+      <c r="A23" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="8" t="s">
         <v>141</v>
       </c>
       <c r="C23" s="10">
         <v>45068</v>
       </c>
-      <c r="D23" s="95">
+      <c r="D23" s="8">
         <v>3</v>
       </c>
       <c r="E23" s="10" t="s">
         <v>154</v>
       </c>
       <c r="F23" s="4"/>
-      <c r="G23" s="97"/>
-      <c r="H23" s="97"/>
-      <c r="I23" s="97"/>
-      <c r="J23" s="95">
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="8">
         <v>0.17610000000000001</v>
       </c>
-      <c r="K23" s="95"/>
-      <c r="L23" s="95"/>
-      <c r="M23" s="95">
+      <c r="M23" s="8">
         <v>56.1</v>
       </c>
-      <c r="N23" s="95">
+      <c r="N23" s="8">
         <v>424</v>
       </c>
-      <c r="O23" s="95">
+      <c r="O23" s="8">
         <v>1509.8</v>
       </c>
       <c r="P23" s="8" t="s">
@@ -4907,21 +4905,21 @@
       <c r="Q23" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="R23" s="115" t="s">
+      <c r="R23" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="S23" s="95"/>
+      <c r="S23" s="8"/>
       <c r="T23" s="16" t="s">
         <v>43</v>
       </c>
       <c r="U23" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V23" s="95" t="s">
+      <c r="V23" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="W23" s="95"/>
-      <c r="X23" s="95"/>
+      <c r="W23" s="8"/>
+      <c r="X23" s="8"/>
       <c r="Y23" s="8"/>
       <c r="Z23" s="16">
         <v>200</v>
@@ -4932,8 +4930,8 @@
       <c r="AB23" s="16">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="AC23" s="95"/>
-      <c r="AD23" s="95">
+      <c r="AC23" s="8"/>
+      <c r="AD23" s="8">
         <v>25.8</v>
       </c>
       <c r="AE23" s="34">
@@ -4950,72 +4948,70 @@
       </c>
     </row>
     <row r="24" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C24" s="97">
+      <c r="C24" s="10">
         <v>45068</v>
       </c>
-      <c r="D24" s="95">
+      <c r="D24" s="8">
         <v>4</v>
       </c>
-      <c r="E24" s="97" t="s">
+      <c r="E24" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="F24" s="98"/>
-      <c r="G24" s="97"/>
-      <c r="H24" s="97"/>
-      <c r="I24" s="97"/>
-      <c r="J24" s="95">
+      <c r="F24" s="4"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="8">
         <v>0.1754</v>
       </c>
-      <c r="K24" s="95"/>
-      <c r="L24" s="95"/>
-      <c r="M24" s="95">
+      <c r="M24" s="8">
         <v>57</v>
       </c>
-      <c r="N24" s="95">
+      <c r="N24" s="8">
         <v>442</v>
       </c>
-      <c r="O24" s="95">
+      <c r="O24" s="8">
         <v>1508.9</v>
       </c>
-      <c r="P24" s="95" t="s">
+      <c r="P24" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="Q24" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="R24" s="115" t="s">
+      <c r="Q24" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="S24" s="95"/>
-      <c r="T24" s="115" t="s">
+      <c r="S24" s="8"/>
+      <c r="T24" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="U24" s="95" t="s">
+      <c r="U24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V24" s="95" t="s">
+      <c r="V24" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="W24" s="95"/>
-      <c r="X24" s="95"/>
-      <c r="Y24" s="95"/>
-      <c r="Z24" s="115">
-        <v>200</v>
-      </c>
-      <c r="AA24" s="95">
+      <c r="W24" s="8"/>
+      <c r="X24" s="8"/>
+      <c r="Y24" s="8"/>
+      <c r="Z24" s="16">
+        <v>200</v>
+      </c>
+      <c r="AA24" s="8">
         <v>111.6</v>
       </c>
-      <c r="AB24" s="115">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="AC24" s="95"/>
-      <c r="AD24" s="95">
+      <c r="AB24" s="16">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC24" s="8"/>
+      <c r="AD24" s="8">
         <v>26</v>
       </c>
       <c r="AE24" s="34">
@@ -5032,71 +5028,69 @@
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A25" s="95" t="s">
+      <c r="A25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="97">
+      <c r="C25" s="10">
         <v>45068</v>
       </c>
-      <c r="D25" s="95">
+      <c r="D25" s="8">
         <v>5</v>
       </c>
-      <c r="E25" s="97" t="s">
+      <c r="E25" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F25" s="98"/>
-      <c r="G25" s="97"/>
-      <c r="H25" s="97"/>
-      <c r="I25" s="97"/>
-      <c r="J25" s="95">
+      <c r="F25" s="4"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="8">
         <v>0.17269999999999999</v>
       </c>
-      <c r="K25" s="95"/>
-      <c r="L25" s="95"/>
-      <c r="M25" s="95">
+      <c r="M25" s="8">
         <v>57.4</v>
       </c>
-      <c r="N25" s="95">
+      <c r="N25" s="8">
         <v>445</v>
       </c>
-      <c r="O25" s="95">
+      <c r="O25" s="8">
         <v>1509.2</v>
       </c>
-      <c r="P25" s="95" t="s">
+      <c r="P25" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="Q25" s="115" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25" s="115" t="s">
+      <c r="Q25" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="S25" s="95"/>
-      <c r="T25" s="115" t="s">
+      <c r="S25" s="8"/>
+      <c r="T25" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="U25" s="95" t="s">
+      <c r="U25" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V25" s="95" t="s">
+      <c r="V25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="W25" s="95"/>
-      <c r="X25" s="95"/>
-      <c r="Y25" s="95"/>
-      <c r="Z25" s="115">
-        <v>200</v>
-      </c>
-      <c r="AA25" s="95">
+      <c r="W25" s="8"/>
+      <c r="X25" s="8"/>
+      <c r="Y25" s="8"/>
+      <c r="Z25" s="16">
+        <v>200</v>
+      </c>
+      <c r="AA25" s="8">
         <v>111.6</v>
       </c>
-      <c r="AB25" s="115">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="AC25" s="95"/>
+      <c r="AB25" s="16">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC25" s="8"/>
       <c r="AD25" s="8">
         <v>26.3</v>
       </c>
@@ -5180,13 +5174,13 @@
       <c r="AD26" s="8">
         <v>26.5</v>
       </c>
-      <c r="AE26" s="95">
+      <c r="AE26" s="8">
         <v>1000</v>
       </c>
-      <c r="AF26" s="103">
+      <c r="AF26" s="36">
         <v>0.46</v>
       </c>
-      <c r="AG26" s="95">
+      <c r="AG26" s="8">
         <v>1.1559999999999999</v>
       </c>
       <c r="AH26" s="3">
@@ -6038,75 +6032,75 @@
       </c>
     </row>
     <row r="37" spans="1:34" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="95" t="s">
+      <c r="A37" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B37" s="95" t="s">
+      <c r="B37" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C37" s="97">
+      <c r="C37" s="10">
         <v>45037</v>
       </c>
-      <c r="D37" s="95">
+      <c r="D37" s="8">
         <v>8</v>
       </c>
-      <c r="E37" s="98" t="s">
+      <c r="E37" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F37" s="98"/>
-      <c r="G37" s="97"/>
-      <c r="H37" s="97"/>
-      <c r="I37" s="100">
+      <c r="F37" s="4"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="26">
         <v>0.184</v>
       </c>
-      <c r="J37" s="95">
+      <c r="J37" s="8">
         <v>0.17760000000000001</v>
       </c>
-      <c r="K37" s="103">
+      <c r="K37" s="36">
         <v>2.4799999999999999E-2</v>
       </c>
-      <c r="L37" s="95">
+      <c r="L37" s="8">
         <v>15</v>
       </c>
-      <c r="M37" s="95">
+      <c r="M37" s="8">
         <v>57.2</v>
       </c>
-      <c r="N37" s="95">
+      <c r="N37" s="8">
         <v>445</v>
       </c>
-      <c r="O37" s="104">
+      <c r="O37" s="39">
         <v>1507.5</v>
       </c>
-      <c r="P37" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q37" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="R37" s="105"/>
-      <c r="S37" s="95" t="s">
+      <c r="P37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" s="5"/>
+      <c r="S37" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="T37" s="105"/>
-      <c r="U37" s="104" t="s">
+      <c r="T37" s="5"/>
+      <c r="U37" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="V37" s="104" t="s">
+      <c r="V37" s="39" t="s">
         <v>172</v>
       </c>
-      <c r="W37" s="105"/>
-      <c r="X37" s="96"/>
-      <c r="Y37" s="95"/>
-      <c r="Z37" s="95">
-        <v>200</v>
-      </c>
-      <c r="AA37" s="95">
+      <c r="W37" s="5"/>
+      <c r="X37" s="3"/>
+      <c r="Y37" s="8"/>
+      <c r="Z37" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA37" s="8">
         <v>111.6</v>
       </c>
-      <c r="AB37" s="95">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="AC37" s="96"/>
+      <c r="AB37" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC37" s="3"/>
       <c r="AD37" s="33" t="s">
         <v>181</v>
       </c>
@@ -8554,7 +8548,7 @@
       </c>
       <c r="G65" s="10"/>
       <c r="H65" s="10"/>
-      <c r="I65" s="97"/>
+      <c r="I65" s="10"/>
       <c r="J65" s="27">
         <v>0.1908</v>
       </c>
@@ -8648,7 +8642,7 @@
       </c>
       <c r="G66" s="10"/>
       <c r="H66" s="10"/>
-      <c r="I66" s="97"/>
+      <c r="I66" s="10"/>
       <c r="J66" s="27">
         <v>0.18479999999999999</v>
       </c>
@@ -8738,7 +8732,7 @@
       </c>
       <c r="G67" s="10"/>
       <c r="H67" s="10"/>
-      <c r="I67" s="97"/>
+      <c r="I67" s="10"/>
       <c r="J67" s="27">
         <v>0.18690000000000001</v>
       </c>
@@ -8832,7 +8826,7 @@
       </c>
       <c r="G68" s="10"/>
       <c r="H68" s="10"/>
-      <c r="I68" s="97"/>
+      <c r="I68" s="10"/>
       <c r="J68" s="27">
         <v>0.18179999999999999</v>
       </c>
@@ -8922,7 +8916,7 @@
       </c>
       <c r="G69" s="10"/>
       <c r="H69" s="10"/>
-      <c r="I69" s="97"/>
+      <c r="I69" s="10"/>
       <c r="J69" s="27">
         <v>0.18540000000000001</v>
       </c>
@@ -9016,7 +9010,7 @@
       </c>
       <c r="G70" s="10"/>
       <c r="H70" s="10"/>
-      <c r="I70" s="97"/>
+      <c r="I70" s="10"/>
       <c r="J70" s="27">
         <v>0.18160000000000001</v>
       </c>
@@ -9106,7 +9100,7 @@
       </c>
       <c r="G71" s="10"/>
       <c r="H71" s="10"/>
-      <c r="I71" s="97"/>
+      <c r="I71" s="10"/>
       <c r="J71" s="27">
         <v>0.184</v>
       </c>
@@ -9200,7 +9194,7 @@
       </c>
       <c r="G72" s="10"/>
       <c r="H72" s="10"/>
-      <c r="I72" s="97"/>
+      <c r="I72" s="10"/>
       <c r="J72" s="27">
         <v>0.1857</v>
       </c>
@@ -9290,7 +9284,7 @@
       </c>
       <c r="G73" s="10"/>
       <c r="H73" s="10"/>
-      <c r="I73" s="97"/>
+      <c r="I73" s="10"/>
       <c r="J73" s="27">
         <v>0.1832</v>
       </c>
@@ -9384,7 +9378,7 @@
       </c>
       <c r="G74" s="10"/>
       <c r="H74" s="10"/>
-      <c r="I74" s="97"/>
+      <c r="I74" s="10"/>
       <c r="J74" s="27">
         <v>0.18410000000000001</v>
       </c>
@@ -10567,10 +10561,10 @@
       <c r="AE87" s="58">
         <v>1007</v>
       </c>
-      <c r="AF87" s="108">
+      <c r="AF87" s="98">
         <v>0.61</v>
       </c>
-      <c r="AG87" s="106">
+      <c r="AG87" s="96">
         <v>1.1619999999999999</v>
       </c>
       <c r="AH87" s="3">
@@ -10651,10 +10645,10 @@
       <c r="AE88" s="58">
         <v>1008</v>
       </c>
-      <c r="AF88" s="108">
+      <c r="AF88" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG88" s="106">
+      <c r="AG88" s="96">
         <v>1.1639999999999999</v>
       </c>
       <c r="AH88" s="3">
@@ -10737,10 +10731,10 @@
       <c r="AE89" s="58">
         <v>1007</v>
       </c>
-      <c r="AF89" s="108">
+      <c r="AF89" s="98">
         <v>0.61</v>
       </c>
-      <c r="AG89" s="106">
+      <c r="AG89" s="96">
         <v>1.1619999999999999</v>
       </c>
       <c r="AH89" s="3">
@@ -10821,10 +10815,10 @@
       <c r="AE90" s="58">
         <v>1007</v>
       </c>
-      <c r="AF90" s="108">
+      <c r="AF90" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG90" s="106">
+      <c r="AG90" s="96">
         <v>1.1619999999999999</v>
       </c>
       <c r="AH90" s="3">
@@ -10902,13 +10896,13 @@
       <c r="AD91" s="8">
         <v>26.4</v>
       </c>
-      <c r="AE91" s="106">
+      <c r="AE91" s="96">
         <v>1007</v>
       </c>
-      <c r="AF91" s="108">
+      <c r="AF91" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG91" s="106">
+      <c r="AG91" s="96">
         <v>1.1619999999999999</v>
       </c>
       <c r="AH91" s="3">
@@ -10988,13 +10982,13 @@
       <c r="AD92" s="8">
         <v>26.5</v>
       </c>
-      <c r="AE92" s="106">
+      <c r="AE92" s="96">
         <v>1007</v>
       </c>
-      <c r="AF92" s="108">
+      <c r="AF92" s="98">
         <v>0.61</v>
       </c>
-      <c r="AG92" s="106">
+      <c r="AG92" s="96">
         <v>1.1619999999999999</v>
       </c>
       <c r="AH92" s="3">
@@ -11074,13 +11068,13 @@
       <c r="AD93" s="8">
         <v>26.5</v>
       </c>
-      <c r="AE93" s="106">
+      <c r="AE93" s="96">
         <v>1007</v>
       </c>
-      <c r="AF93" s="108">
+      <c r="AF93" s="98">
         <v>0.61</v>
       </c>
-      <c r="AG93" s="106">
+      <c r="AG93" s="96">
         <v>1.1619999999999999</v>
       </c>
       <c r="AH93" s="3">
@@ -11158,13 +11152,13 @@
       <c r="AD94" s="8">
         <v>26.7</v>
       </c>
-      <c r="AE94" s="106">
+      <c r="AE94" s="96">
         <v>1008</v>
       </c>
-      <c r="AF94" s="108">
+      <c r="AF94" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG94" s="106">
+      <c r="AG94" s="96">
         <v>1.161</v>
       </c>
       <c r="AH94" s="3">
@@ -11244,13 +11238,13 @@
       <c r="AD95" s="8">
         <v>27</v>
       </c>
-      <c r="AE95" s="106">
+      <c r="AE95" s="96">
         <v>1007</v>
       </c>
-      <c r="AF95" s="108">
+      <c r="AF95" s="98">
         <v>0.61</v>
       </c>
-      <c r="AG95" s="106">
+      <c r="AG95" s="96">
         <v>1.159</v>
       </c>
       <c r="AH95" s="3">
@@ -11330,13 +11324,13 @@
       <c r="AD96" s="8">
         <v>27</v>
       </c>
-      <c r="AE96" s="106">
+      <c r="AE96" s="96">
         <v>1007</v>
       </c>
-      <c r="AF96" s="108">
+      <c r="AF96" s="98">
         <v>0.6</v>
       </c>
-      <c r="AG96" s="106">
+      <c r="AG96" s="96">
         <v>1.159</v>
       </c>
       <c r="AH96" s="3">
@@ -11416,13 +11410,13 @@
       <c r="AD97" s="8">
         <v>24.5</v>
       </c>
-      <c r="AE97" s="106">
+      <c r="AE97" s="96">
         <v>1007</v>
       </c>
-      <c r="AF97" s="108">
+      <c r="AF97" s="98">
         <v>0.65</v>
       </c>
-      <c r="AG97" s="106">
+      <c r="AG97" s="96">
         <v>1.169</v>
       </c>
       <c r="AH97" s="3">
@@ -11502,13 +11496,13 @@
       <c r="AD98" s="8">
         <v>25.2</v>
       </c>
-      <c r="AE98" s="106">
+      <c r="AE98" s="96">
         <v>1006</v>
       </c>
-      <c r="AF98" s="108">
+      <c r="AF98" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG98" s="106">
+      <c r="AG98" s="96">
         <v>1.1659999999999999</v>
       </c>
       <c r="AH98" s="3">
@@ -11588,13 +11582,13 @@
       <c r="AD99" s="8">
         <v>24.7</v>
       </c>
-      <c r="AE99" s="106">
+      <c r="AE99" s="96">
         <v>1007</v>
       </c>
-      <c r="AF99" s="108">
+      <c r="AF99" s="98">
         <v>0.65</v>
       </c>
-      <c r="AG99" s="106">
+      <c r="AG99" s="96">
         <v>1.1679999999999999</v>
       </c>
       <c r="AH99" s="3">
@@ -11674,13 +11668,13 @@
       <c r="AD100" s="8">
         <v>25.2</v>
       </c>
-      <c r="AE100" s="106">
+      <c r="AE100" s="96">
         <v>1006</v>
       </c>
-      <c r="AF100" s="108">
+      <c r="AF100" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG100" s="106">
+      <c r="AG100" s="96">
         <v>1.1659999999999999</v>
       </c>
       <c r="AH100" s="3">
@@ -11760,13 +11754,13 @@
       <c r="AD101" s="8">
         <v>25.3</v>
       </c>
-      <c r="AE101" s="106">
+      <c r="AE101" s="96">
         <v>1006</v>
       </c>
-      <c r="AF101" s="108">
+      <c r="AF101" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG101" s="106">
+      <c r="AG101" s="96">
         <v>1.165</v>
       </c>
       <c r="AH101" s="3">
@@ -11846,13 +11840,13 @@
       <c r="AD102" s="8">
         <v>25.3</v>
       </c>
-      <c r="AE102" s="106">
+      <c r="AE102" s="96">
         <v>1006</v>
       </c>
-      <c r="AF102" s="108">
+      <c r="AF102" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG102" s="106">
+      <c r="AG102" s="96">
         <v>1.165</v>
       </c>
       <c r="AH102" s="3">
@@ -11932,13 +11926,13 @@
       <c r="AD103" s="8">
         <v>25.4</v>
       </c>
-      <c r="AE103" s="106">
+      <c r="AE103" s="96">
         <v>1006</v>
       </c>
-      <c r="AF103" s="108">
+      <c r="AF103" s="98">
         <v>0.63</v>
       </c>
-      <c r="AG103" s="106">
+      <c r="AG103" s="96">
         <v>1.165</v>
       </c>
       <c r="AH103" s="3">
@@ -13756,7 +13750,7 @@
       <c r="F125" s="10"/>
       <c r="G125" s="10"/>
       <c r="H125" s="10"/>
-      <c r="I125" s="97"/>
+      <c r="I125" s="10"/>
       <c r="J125" s="8">
         <v>0.21299999999999999</v>
       </c>
@@ -13842,7 +13836,7 @@
       <c r="F126" s="10"/>
       <c r="G126" s="10"/>
       <c r="H126" s="10"/>
-      <c r="I126" s="97"/>
+      <c r="I126" s="10"/>
       <c r="J126" s="8">
         <v>0.20150000000000001</v>
       </c>
@@ -13928,7 +13922,7 @@
       <c r="F127" s="10"/>
       <c r="G127" s="10"/>
       <c r="H127" s="10"/>
-      <c r="I127" s="97"/>
+      <c r="I127" s="10"/>
       <c r="J127" s="8">
         <v>0.1996</v>
       </c>
@@ -14014,7 +14008,7 @@
       <c r="F128" s="10"/>
       <c r="G128" s="10"/>
       <c r="H128" s="10"/>
-      <c r="I128" s="97"/>
+      <c r="I128" s="10"/>
       <c r="J128" s="8">
         <v>0.21429999999999999</v>
       </c>
@@ -14094,7 +14088,7 @@
       <c r="F129" s="10"/>
       <c r="G129" s="10"/>
       <c r="H129" s="10"/>
-      <c r="I129" s="97"/>
+      <c r="I129" s="10"/>
       <c r="J129" s="8">
         <v>0.17119999999999999</v>
       </c>
@@ -14178,7 +14172,7 @@
       <c r="F130" s="10"/>
       <c r="G130" s="10"/>
       <c r="H130" s="10"/>
-      <c r="I130" s="97"/>
+      <c r="I130" s="10"/>
       <c r="J130" s="8">
         <v>0.21490000000000001</v>
       </c>
@@ -14258,7 +14252,7 @@
       <c r="F131" s="10"/>
       <c r="G131" s="10"/>
       <c r="H131" s="10"/>
-      <c r="I131" s="97"/>
+      <c r="I131" s="10"/>
       <c r="J131" s="8">
         <v>0.16950000000000001</v>
       </c>
@@ -14342,7 +14336,7 @@
       <c r="F132" s="10"/>
       <c r="G132" s="10"/>
       <c r="H132" s="10"/>
-      <c r="I132" s="97"/>
+      <c r="I132" s="10"/>
       <c r="J132" s="8">
         <v>0.21540000000000001</v>
       </c>
@@ -14422,7 +14416,7 @@
       <c r="F133" s="10"/>
       <c r="G133" s="10"/>
       <c r="H133" s="10"/>
-      <c r="I133" s="97"/>
+      <c r="I133" s="10"/>
       <c r="J133" s="8">
         <v>0.1618</v>
       </c>
@@ -14506,7 +14500,7 @@
       <c r="F134" s="10"/>
       <c r="G134" s="10"/>
       <c r="H134" s="10"/>
-      <c r="I134" s="97"/>
+      <c r="I134" s="10"/>
       <c r="J134" s="8">
         <v>0.21529999999999999</v>
       </c>
@@ -15506,10 +15500,10 @@
       <c r="J146" s="8">
         <v>0.18840000000000001</v>
       </c>
-      <c r="K146" s="103">
+      <c r="K146" s="36">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="L146" s="95">
+      <c r="L146" s="8">
         <v>33</v>
       </c>
       <c r="M146" s="8">
@@ -15592,10 +15586,10 @@
       <c r="J147" s="8">
         <v>0.18740000000000001</v>
       </c>
-      <c r="K147" s="103">
+      <c r="K147" s="36">
         <v>4.9700000000000001E-2</v>
       </c>
-      <c r="L147" s="95">
+      <c r="L147" s="8">
         <v>33</v>
       </c>
       <c r="M147" s="8">
@@ -17666,73 +17660,73 @@
       </c>
     </row>
     <row r="172" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A172" s="95" t="s">
+      <c r="A172" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B172" s="95" t="s">
+      <c r="B172" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C172" s="97">
+      <c r="C172" s="10">
         <v>44888</v>
       </c>
-      <c r="D172" s="95">
+      <c r="D172" s="8">
         <v>5</v>
       </c>
-      <c r="E172" s="97" t="s">
+      <c r="E172" s="10" t="s">
         <v>221</v>
       </c>
       <c r="F172" s="10"/>
-      <c r="G172" s="97"/>
-      <c r="H172" s="97"/>
-      <c r="I172" s="97"/>
+      <c r="G172" s="10"/>
+      <c r="H172" s="10"/>
+      <c r="I172" s="10"/>
       <c r="J172" s="8">
         <v>0.16800000000000001</v>
       </c>
-      <c r="K172" s="103">
+      <c r="K172" s="36">
         <v>1.4500000000000001E-2</v>
       </c>
-      <c r="L172" s="95">
+      <c r="L172" s="8">
         <v>8</v>
       </c>
-      <c r="M172" s="95">
+      <c r="M172" s="8">
         <v>58.7</v>
       </c>
-      <c r="N172" s="95">
+      <c r="N172" s="8">
         <v>450</v>
       </c>
-      <c r="O172" s="95">
+      <c r="O172" s="8">
         <v>1510.5</v>
       </c>
-      <c r="P172" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q172" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="R172" s="95" t="s">
+      <c r="P172" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q172" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R172" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="S172" s="105"/>
-      <c r="T172" s="95" t="s">
+      <c r="S172" s="5"/>
+      <c r="T172" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="U172" s="95" t="s">
+      <c r="U172" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="V172" s="95"/>
-      <c r="W172" s="95"/>
-      <c r="X172" s="104"/>
-      <c r="Y172" s="104"/>
-      <c r="Z172" s="95">
-        <v>200</v>
-      </c>
-      <c r="AA172" s="95">
+      <c r="V172" s="8"/>
+      <c r="W172" s="8"/>
+      <c r="X172" s="39"/>
+      <c r="Y172" s="39"/>
+      <c r="Z172" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA172" s="8">
         <v>111.6</v>
       </c>
-      <c r="AB172" s="95">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="AC172" s="96"/>
+      <c r="AB172" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC172" s="3"/>
       <c r="AD172" s="33" t="s">
         <v>84</v>
       </c>
@@ -18350,7 +18344,7 @@
       <c r="F180" s="10"/>
       <c r="G180" s="10"/>
       <c r="H180" s="10"/>
-      <c r="I180" s="97"/>
+      <c r="I180" s="10"/>
       <c r="J180" s="8">
         <v>0.17330000000000001</v>
       </c>
@@ -18436,7 +18430,7 @@
       <c r="F181" s="10"/>
       <c r="G181" s="10"/>
       <c r="H181" s="10"/>
-      <c r="I181" s="97"/>
+      <c r="I181" s="10"/>
       <c r="J181" s="8">
         <v>0.17319999999999999</v>
       </c>
@@ -18522,7 +18516,7 @@
       <c r="F182" s="10"/>
       <c r="G182" s="10"/>
       <c r="H182" s="10"/>
-      <c r="I182" s="97"/>
+      <c r="I182" s="10"/>
       <c r="J182" s="8">
         <v>0.19400000000000001</v>
       </c>
@@ -18608,7 +18602,7 @@
       <c r="F183" s="10"/>
       <c r="G183" s="10"/>
       <c r="H183" s="10"/>
-      <c r="I183" s="97"/>
+      <c r="I183" s="10"/>
       <c r="J183" s="8">
         <v>0.1875</v>
       </c>
@@ -18694,7 +18688,7 @@
       <c r="F184" s="10"/>
       <c r="G184" s="10"/>
       <c r="H184" s="10"/>
-      <c r="I184" s="97"/>
+      <c r="I184" s="10"/>
       <c r="J184" s="8">
         <v>0.18140000000000001</v>
       </c>
@@ -18780,7 +18774,7 @@
       <c r="F185" s="10"/>
       <c r="G185" s="10"/>
       <c r="H185" s="10"/>
-      <c r="I185" s="97"/>
+      <c r="I185" s="10"/>
       <c r="J185" s="8">
         <v>0.18099999999999999</v>
       </c>
@@ -18866,7 +18860,7 @@
       <c r="F186" s="10"/>
       <c r="G186" s="10"/>
       <c r="H186" s="10"/>
-      <c r="I186" s="97"/>
+      <c r="I186" s="10"/>
       <c r="J186" s="8">
         <v>0.18579999999999999</v>
       </c>
@@ -18952,7 +18946,7 @@
       <c r="F187" s="10"/>
       <c r="G187" s="10"/>
       <c r="H187" s="10"/>
-      <c r="I187" s="97"/>
+      <c r="I187" s="10"/>
       <c r="J187" s="8">
         <v>0.1852</v>
       </c>
@@ -19035,7 +19029,6 @@
       <c r="E188" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I188" s="95"/>
       <c r="J188" s="8">
         <v>0.20549999999999999</v>
       </c>
@@ -21201,7 +21194,7 @@
       </c>
       <c r="G214" s="10"/>
       <c r="H214" s="10"/>
-      <c r="I214" s="97"/>
+      <c r="I214" s="10"/>
       <c r="J214" s="8">
         <v>0.19170000000000001</v>
       </c>
@@ -21287,7 +21280,7 @@
       </c>
       <c r="G215" s="10"/>
       <c r="H215" s="10"/>
-      <c r="I215" s="97"/>
+      <c r="I215" s="10"/>
       <c r="J215" s="8">
         <v>0.19070000000000001</v>
       </c>
@@ -21373,7 +21366,7 @@
       </c>
       <c r="G216" s="10"/>
       <c r="H216" s="10"/>
-      <c r="I216" s="97"/>
+      <c r="I216" s="10"/>
       <c r="J216" s="8">
         <v>0.19040000000000001</v>
       </c>
@@ -21457,7 +21450,6 @@
       <c r="F217" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="I217" s="95"/>
       <c r="J217" s="8">
         <v>0.22850000000000001</v>
       </c>
@@ -21541,7 +21533,7 @@
       </c>
       <c r="G218" s="10"/>
       <c r="H218" s="10"/>
-      <c r="I218" s="97"/>
+      <c r="I218" s="10"/>
       <c r="J218" s="8">
         <v>0.18870000000000001</v>
       </c>
@@ -22197,69 +22189,69 @@
       </c>
     </row>
     <row r="226" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A226" s="95" t="s">
+      <c r="A226" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B226" s="95" t="s">
+      <c r="B226" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="C226" s="97">
+      <c r="C226" s="10">
         <v>44888</v>
       </c>
-      <c r="D226" s="95">
+      <c r="D226" s="8">
         <v>1</v>
       </c>
-      <c r="E226" s="97" t="s">
+      <c r="E226" s="10" t="s">
         <v>129</v>
       </c>
       <c r="F226" s="10"/>
-      <c r="G226" s="97"/>
-      <c r="H226" s="97"/>
-      <c r="I226" s="97"/>
+      <c r="G226" s="10"/>
+      <c r="H226" s="10"/>
+      <c r="I226" s="10"/>
       <c r="J226" s="8">
         <v>0.2268</v>
       </c>
-      <c r="K226" s="97" t="s">
+      <c r="K226" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="L226" s="97" t="s">
+      <c r="L226" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="M226" s="95">
+      <c r="M226" s="8">
         <v>54.7</v>
       </c>
-      <c r="N226" s="95">
+      <c r="N226" s="8">
         <v>478</v>
       </c>
-      <c r="O226" s="95">
+      <c r="O226" s="8">
         <v>1512.4</v>
       </c>
-      <c r="P226" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q226" s="95" t="s">
-        <v>20</v>
-      </c>
-      <c r="R226" s="95"/>
-      <c r="S226" s="95"/>
-      <c r="T226" s="95"/>
-      <c r="U226" s="95" t="s">
+      <c r="P226" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q226" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="R226" s="8"/>
+      <c r="S226" s="8"/>
+      <c r="T226" s="8"/>
+      <c r="U226" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="V226" s="95"/>
-      <c r="W226" s="95"/>
-      <c r="X226" s="95"/>
-      <c r="Y226" s="95"/>
-      <c r="Z226" s="95">
-        <v>200</v>
-      </c>
-      <c r="AA226" s="95">
+      <c r="V226" s="8"/>
+      <c r="W226" s="8"/>
+      <c r="X226" s="8"/>
+      <c r="Y226" s="8"/>
+      <c r="Z226" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA226" s="8">
         <v>108</v>
       </c>
-      <c r="AB226" s="95">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="AC226" s="96"/>
+      <c r="AB226" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC226" s="3"/>
       <c r="AD226" s="33" t="s">
         <v>86</v>
       </c>
@@ -22854,7 +22846,7 @@
       </c>
       <c r="G234" s="10"/>
       <c r="H234" s="10"/>
-      <c r="I234" s="97"/>
+      <c r="I234" s="10"/>
       <c r="J234" s="8">
         <v>0.2029</v>
       </c>
@@ -23579,9 +23571,9 @@
         <v>76</v>
       </c>
       <c r="F243" s="4"/>
-      <c r="G243" s="110"/>
-      <c r="H243" s="110"/>
-      <c r="I243" s="110"/>
+      <c r="G243" s="100"/>
+      <c r="H243" s="100"/>
+      <c r="I243" s="100"/>
       <c r="J243" s="85">
         <v>0.17949999999999999</v>
       </c>
@@ -23589,7 +23581,7 @@
       <c r="L243" s="45"/>
       <c r="M243" s="45"/>
       <c r="N243" s="45"/>
-      <c r="O243" s="114"/>
+      <c r="O243" s="101"/>
       <c r="P243" s="71" t="s">
         <v>347</v>
       </c>
@@ -23636,8 +23628,8 @@
       <c r="AE243" s="87">
         <v>1003</v>
       </c>
-      <c r="AF243" s="117"/>
-      <c r="AG243" s="107"/>
+      <c r="AF243" s="102"/>
+      <c r="AG243" s="97"/>
       <c r="AH243" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -23716,8 +23708,8 @@
       <c r="AE244" s="87">
         <v>1003</v>
       </c>
-      <c r="AF244" s="117"/>
-      <c r="AG244" s="107"/>
+      <c r="AF244" s="102"/>
+      <c r="AG244" s="97"/>
       <c r="AH244" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -23794,8 +23786,8 @@
       <c r="AE245" s="87">
         <v>1003</v>
       </c>
-      <c r="AF245" s="117"/>
-      <c r="AG245" s="107"/>
+      <c r="AF245" s="102"/>
+      <c r="AG245" s="97"/>
       <c r="AH245" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -23872,8 +23864,8 @@
       <c r="AE246" s="87">
         <v>1003</v>
       </c>
-      <c r="AF246" s="117"/>
-      <c r="AG246" s="107"/>
+      <c r="AF246" s="102"/>
+      <c r="AG246" s="97"/>
       <c r="AH246" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -23950,8 +23942,8 @@
       <c r="AE247" s="87">
         <v>1003</v>
       </c>
-      <c r="AF247" s="117"/>
-      <c r="AG247" s="107"/>
+      <c r="AF247" s="102"/>
+      <c r="AG247" s="97"/>
       <c r="AH247" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24030,8 +24022,8 @@
       <c r="AE248" s="87">
         <v>1003</v>
       </c>
-      <c r="AF248" s="117"/>
-      <c r="AG248" s="107"/>
+      <c r="AF248" s="102"/>
+      <c r="AG248" s="97"/>
       <c r="AH248" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24104,8 +24096,8 @@
       <c r="AE249" s="34">
         <v>1012</v>
       </c>
-      <c r="AF249" s="117"/>
-      <c r="AG249" s="95"/>
+      <c r="AF249" s="102"/>
+      <c r="AG249" s="8"/>
       <c r="AH249" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24178,8 +24170,8 @@
       <c r="AE250" s="34">
         <v>1012</v>
       </c>
-      <c r="AF250" s="117"/>
-      <c r="AG250" s="95"/>
+      <c r="AF250" s="102"/>
+      <c r="AG250" s="8"/>
       <c r="AH250" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24252,8 +24244,8 @@
       <c r="AE251" s="34">
         <v>1012</v>
       </c>
-      <c r="AF251" s="117"/>
-      <c r="AG251" s="95"/>
+      <c r="AF251" s="102"/>
+      <c r="AG251" s="8"/>
       <c r="AH251" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24326,8 +24318,8 @@
       <c r="AE252" s="34">
         <v>1012</v>
       </c>
-      <c r="AF252" s="117"/>
-      <c r="AG252" s="95"/>
+      <c r="AF252" s="102"/>
+      <c r="AG252" s="8"/>
       <c r="AH252" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24400,8 +24392,8 @@
       <c r="AE253" s="34">
         <v>1012</v>
       </c>
-      <c r="AF253" s="117"/>
-      <c r="AG253" s="95"/>
+      <c r="AF253" s="102"/>
+      <c r="AG253" s="8"/>
       <c r="AH253" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24477,11 +24469,11 @@
       <c r="AD254" s="27">
         <v>22.8</v>
       </c>
-      <c r="AE254" s="102">
+      <c r="AE254" s="95">
         <v>1012</v>
       </c>
-      <c r="AF254" s="117"/>
-      <c r="AG254" s="95"/>
+      <c r="AF254" s="102"/>
+      <c r="AG254" s="8"/>
       <c r="AH254" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24557,11 +24549,11 @@
       <c r="AD255" s="27">
         <v>22.8</v>
       </c>
-      <c r="AE255" s="102">
+      <c r="AE255" s="95">
         <v>1012</v>
       </c>
-      <c r="AF255" s="117"/>
-      <c r="AG255" s="95"/>
+      <c r="AF255" s="102"/>
+      <c r="AG255" s="8"/>
       <c r="AH255" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24596,7 +24588,7 @@
       <c r="K256" s="45"/>
       <c r="L256" s="45"/>
       <c r="M256" s="45"/>
-      <c r="N256" s="102">
+      <c r="N256" s="95">
         <v>421</v>
       </c>
       <c r="O256" s="45"/>
@@ -24637,11 +24629,11 @@
       <c r="AD256" s="27">
         <v>22.8</v>
       </c>
-      <c r="AE256" s="102">
+      <c r="AE256" s="95">
         <v>1012</v>
       </c>
-      <c r="AF256" s="117"/>
-      <c r="AG256" s="95"/>
+      <c r="AF256" s="102"/>
+      <c r="AG256" s="8"/>
       <c r="AH256" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24717,11 +24709,11 @@
       <c r="AD257" s="27">
         <v>22.8</v>
       </c>
-      <c r="AE257" s="102">
+      <c r="AE257" s="95">
         <v>1012</v>
       </c>
-      <c r="AF257" s="117"/>
-      <c r="AG257" s="95"/>
+      <c r="AF257" s="102"/>
+      <c r="AG257" s="8"/>
       <c r="AH257" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24797,11 +24789,11 @@
       <c r="AD258" s="27">
         <v>22.8</v>
       </c>
-      <c r="AE258" s="102">
+      <c r="AE258" s="95">
         <v>1012</v>
       </c>
-      <c r="AF258" s="117"/>
-      <c r="AG258" s="95"/>
+      <c r="AF258" s="102"/>
+      <c r="AG258" s="8"/>
       <c r="AH258" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24883,11 +24875,11 @@
       <c r="AD259" s="27">
         <v>24.6</v>
       </c>
-      <c r="AE259" s="102">
+      <c r="AE259" s="95">
         <v>1005</v>
       </c>
-      <c r="AF259" s="117"/>
-      <c r="AG259" s="116"/>
+      <c r="AF259" s="102"/>
+      <c r="AG259" s="85"/>
       <c r="AH259" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -24969,11 +24961,11 @@
       <c r="AD260" s="27">
         <v>24.6</v>
       </c>
-      <c r="AE260" s="102">
+      <c r="AE260" s="95">
         <v>1005</v>
       </c>
-      <c r="AF260" s="117"/>
-      <c r="AG260" s="116"/>
+      <c r="AF260" s="102"/>
+      <c r="AG260" s="85"/>
       <c r="AH260" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25055,11 +25047,11 @@
       <c r="AD261" s="27">
         <v>25.4</v>
       </c>
-      <c r="AE261" s="102">
+      <c r="AE261" s="95">
         <v>1005</v>
       </c>
-      <c r="AF261" s="117"/>
-      <c r="AG261" s="116"/>
+      <c r="AF261" s="102"/>
+      <c r="AG261" s="85"/>
       <c r="AH261" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25141,11 +25133,11 @@
       <c r="AD262" s="27">
         <v>25.7</v>
       </c>
-      <c r="AE262" s="102">
+      <c r="AE262" s="95">
         <v>1005</v>
       </c>
-      <c r="AF262" s="117"/>
-      <c r="AG262" s="116"/>
+      <c r="AF262" s="102"/>
+      <c r="AG262" s="85"/>
       <c r="AH262" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25225,11 +25217,11 @@
       <c r="AD263" s="27">
         <v>26.2</v>
       </c>
-      <c r="AE263" s="102">
+      <c r="AE263" s="95">
         <v>1005</v>
       </c>
-      <c r="AF263" s="117"/>
-      <c r="AG263" s="116"/>
+      <c r="AF263" s="102"/>
+      <c r="AG263" s="85"/>
       <c r="AH263" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25310,82 +25302,82 @@
       <c r="AE264" s="90">
         <v>1001</v>
       </c>
-      <c r="AF264" s="116">
+      <c r="AF264" s="85">
         <v>48.2</v>
       </c>
-      <c r="AG264" s="119"/>
+      <c r="AG264" s="104"/>
       <c r="AH264" s="3">
         <v>2.0960000000000001</v>
       </c>
     </row>
     <row r="265" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A265" s="95" t="s">
+      <c r="A265" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="B265" s="95" t="s">
+      <c r="B265" s="8" t="s">
         <v>308</v>
       </c>
-      <c r="C265" s="97">
+      <c r="C265" s="10">
         <v>45068</v>
       </c>
-      <c r="D265" s="99">
+      <c r="D265" s="20">
         <v>2</v>
       </c>
-      <c r="E265" s="97" t="s">
+      <c r="E265" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="F265" s="98"/>
-      <c r="G265" s="97"/>
-      <c r="H265" s="97"/>
-      <c r="I265" s="100"/>
-      <c r="J265" s="111">
+      <c r="F265" s="4"/>
+      <c r="G265" s="10"/>
+      <c r="H265" s="10"/>
+      <c r="I265" s="26"/>
+      <c r="J265" s="27">
         <v>0.17760000000000001</v>
       </c>
-      <c r="K265" s="97"/>
-      <c r="L265" s="97"/>
-      <c r="M265" s="111">
+      <c r="K265" s="10"/>
+      <c r="L265" s="10"/>
+      <c r="M265" s="27">
         <v>53.5</v>
       </c>
-      <c r="N265" s="99">
+      <c r="N265" s="20">
         <v>358</v>
       </c>
-      <c r="O265" s="97"/>
-      <c r="P265" s="113"/>
-      <c r="Q265" s="95" t="s">
+      <c r="O265" s="10"/>
+      <c r="P265" s="23"/>
+      <c r="Q265" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="R265" s="105" t="s">
+      <c r="R265" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="S265" s="105" t="s">
+      <c r="S265" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="T265" s="105" t="s">
+      <c r="T265" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="U265" s="105" t="s">
+      <c r="U265" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="V265" s="105" t="s">
+      <c r="V265" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="W265" s="95">
+      <c r="W265" s="8">
         <v>71.7</v>
       </c>
-      <c r="X265" s="95">
+      <c r="X265" s="8">
         <v>8.1999999999999993</v>
       </c>
-      <c r="Y265" s="96"/>
-      <c r="Z265" s="95">
-        <v>200</v>
-      </c>
-      <c r="AA265" s="95" t="s">
+      <c r="Y265" s="3"/>
+      <c r="Z265" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA265" s="8" t="s">
         <v>344</v>
       </c>
-      <c r="AB265" s="95">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="AC265" s="95">
+      <c r="AB265" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC265" s="8">
         <v>99.74</v>
       </c>
       <c r="AD265" s="85">
@@ -25394,10 +25386,10 @@
       <c r="AE265" s="90">
         <v>1001</v>
       </c>
-      <c r="AF265" s="116">
+      <c r="AF265" s="85">
         <v>47.1</v>
       </c>
-      <c r="AG265" s="119"/>
+      <c r="AG265" s="104"/>
       <c r="AH265" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25480,10 +25472,10 @@
       <c r="AE266" s="90">
         <v>1001</v>
       </c>
-      <c r="AF266" s="116">
+      <c r="AF266" s="85">
         <v>46.8</v>
       </c>
-      <c r="AG266" s="119"/>
+      <c r="AG266" s="104"/>
       <c r="AH266" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25566,10 +25558,10 @@
       <c r="AE267" s="90">
         <v>1001</v>
       </c>
-      <c r="AF267" s="116">
+      <c r="AF267" s="85">
         <v>46.5</v>
       </c>
-      <c r="AG267" s="119"/>
+      <c r="AG267" s="104"/>
       <c r="AH267" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25649,59 +25641,59 @@
       <c r="AD268" s="85">
         <v>26.3</v>
       </c>
-      <c r="AE268" s="116">
+      <c r="AE268" s="85">
         <v>1000</v>
       </c>
-      <c r="AF268" s="116">
+      <c r="AF268" s="85">
         <v>46.1</v>
       </c>
-      <c r="AG268" s="119"/>
+      <c r="AG268" s="104"/>
       <c r="AH268" s="3">
         <v>2.0960000000000001</v>
       </c>
     </row>
     <row r="269" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A269" s="95" t="s">
+      <c r="A269" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="B269" s="95" t="s">
+      <c r="B269" s="8" t="s">
         <v>308</v>
       </c>
       <c r="C269" s="10">
         <v>45068</v>
       </c>
-      <c r="D269" s="99">
+      <c r="D269" s="20">
         <v>6</v>
       </c>
       <c r="E269" s="10" t="s">
         <v>311</v>
       </c>
       <c r="F269" s="4"/>
-      <c r="G269" s="97"/>
-      <c r="H269" s="97"/>
-      <c r="I269" s="100">
+      <c r="G269" s="10"/>
+      <c r="H269" s="10"/>
+      <c r="I269" s="26">
         <v>0.17299999999999999</v>
       </c>
-      <c r="J269" s="101">
+      <c r="J269" s="22">
         <v>0.1777</v>
       </c>
-      <c r="K269" s="97"/>
-      <c r="L269" s="97"/>
-      <c r="M269" s="112">
+      <c r="K269" s="10"/>
+      <c r="L269" s="10"/>
+      <c r="M269" s="89">
         <v>54</v>
       </c>
-      <c r="N269" s="99">
+      <c r="N269" s="20">
         <v>364</v>
       </c>
-      <c r="O269" s="97"/>
+      <c r="O269" s="10"/>
       <c r="P269" s="23"/>
       <c r="Q269" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="R269" s="105" t="s">
+      <c r="R269" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="S269" s="105" t="s">
+      <c r="S269" s="5" t="s">
         <v>158</v>
       </c>
       <c r="T269" s="5" t="s">
@@ -25710,13 +25702,13 @@
       <c r="U269" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="V269" s="105" t="s">
+      <c r="V269" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="W269" s="95">
+      <c r="W269" s="8">
         <v>71.5</v>
       </c>
-      <c r="X269" s="95">
+      <c r="X269" s="8">
         <v>8.1999999999999993</v>
       </c>
       <c r="Y269" s="3"/>
@@ -25729,19 +25721,19 @@
       <c r="AB269" s="8">
         <v>2.0999999999999999E-3</v>
       </c>
-      <c r="AC269" s="95">
+      <c r="AC269" s="8">
         <v>99.74</v>
       </c>
       <c r="AD269" s="85">
         <v>26.4</v>
       </c>
-      <c r="AE269" s="116">
+      <c r="AE269" s="85">
         <v>1000</v>
       </c>
-      <c r="AF269" s="116">
+      <c r="AF269" s="85">
         <v>45.6</v>
       </c>
-      <c r="AG269" s="119"/>
+      <c r="AG269" s="104"/>
       <c r="AH269" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25821,13 +25813,13 @@
       <c r="AD270" s="85">
         <v>26.6</v>
       </c>
-      <c r="AE270" s="116">
+      <c r="AE270" s="85">
         <v>1000</v>
       </c>
-      <c r="AF270" s="116">
+      <c r="AF270" s="85">
         <v>46</v>
       </c>
-      <c r="AG270" s="119"/>
+      <c r="AG270" s="104"/>
       <c r="AH270" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -25907,10 +25899,10 @@
       <c r="AD271" s="85">
         <v>26.6</v>
       </c>
-      <c r="AE271" s="116">
+      <c r="AE271" s="85">
         <v>1000</v>
       </c>
-      <c r="AF271" s="116">
+      <c r="AF271" s="85">
         <v>45.7</v>
       </c>
       <c r="AG271" s="84"/>
@@ -25993,10 +25985,10 @@
       <c r="AD272" s="85">
         <v>26.8</v>
       </c>
-      <c r="AE272" s="116">
+      <c r="AE272" s="85">
         <v>999</v>
       </c>
-      <c r="AF272" s="116">
+      <c r="AF272" s="85">
         <v>45.8</v>
       </c>
       <c r="AG272" s="84"/>
@@ -26081,10 +26073,10 @@
       <c r="AD273" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="AE273" s="106">
+      <c r="AE273" s="96">
         <v>1016</v>
       </c>
-      <c r="AF273" s="118"/>
+      <c r="AF273" s="103"/>
       <c r="AG273" s="60"/>
       <c r="AH273" s="3">
         <v>2.0960000000000001</v>
@@ -26167,10 +26159,10 @@
       <c r="AD274" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="AE274" s="95">
+      <c r="AE274" s="8">
         <v>1016</v>
       </c>
-      <c r="AF274" s="118"/>
+      <c r="AF274" s="103"/>
       <c r="AG274" s="52"/>
       <c r="AH274" s="3">
         <v>2.0960000000000001</v>
@@ -26253,10 +26245,10 @@
       <c r="AD275" s="33" t="s">
         <v>212</v>
       </c>
-      <c r="AE275" s="95">
+      <c r="AE275" s="8">
         <v>1016</v>
       </c>
-      <c r="AF275" s="118"/>
+      <c r="AF275" s="103"/>
       <c r="AG275" s="52"/>
       <c r="AH275" s="3">
         <v>2.0960000000000001</v>
@@ -26339,96 +26331,96 @@
       <c r="AD276" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="AE276" s="95">
+      <c r="AE276" s="8">
         <v>1016</v>
       </c>
-      <c r="AF276" s="118"/>
+      <c r="AF276" s="103"/>
       <c r="AG276" s="52"/>
       <c r="AH276" s="3">
         <v>2.0960000000000001</v>
       </c>
     </row>
     <row r="277" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A277" s="95" t="s">
+      <c r="A277" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="B277" s="95" t="s">
+      <c r="B277" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="C277" s="97">
+      <c r="C277" s="10">
         <v>45061</v>
       </c>
-      <c r="D277" s="99">
+      <c r="D277" s="20">
         <v>5</v>
       </c>
-      <c r="E277" s="97" t="s">
+      <c r="E277" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="F277" s="98" t="s">
+      <c r="F277" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="G277" s="97"/>
-      <c r="H277" s="97"/>
-      <c r="I277" s="100">
+      <c r="G277" s="10"/>
+      <c r="H277" s="10"/>
+      <c r="I277" s="26">
         <v>0.17799999999999999</v>
       </c>
-      <c r="J277" s="101">
+      <c r="J277" s="22">
         <v>0.1855</v>
       </c>
-      <c r="K277" s="97"/>
-      <c r="L277" s="97"/>
-      <c r="M277" s="97"/>
-      <c r="N277" s="97"/>
-      <c r="O277" s="113"/>
-      <c r="P277" s="105" t="s">
+      <c r="K277" s="10"/>
+      <c r="L277" s="10"/>
+      <c r="M277" s="10"/>
+      <c r="N277" s="10"/>
+      <c r="O277" s="23"/>
+      <c r="P277" s="5" t="s">
         <v>364</v>
       </c>
-      <c r="Q277" s="105" t="s">
-        <v>20</v>
-      </c>
-      <c r="R277" s="105" t="s">
+      <c r="Q277" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R277" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="S277" s="105" t="s">
+      <c r="S277" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="T277" s="105" t="s">
+      <c r="T277" s="5" t="s">
         <v>357</v>
       </c>
-      <c r="U277" s="105" t="s">
+      <c r="U277" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="V277" s="105" t="s">
+      <c r="V277" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="W277" s="95">
+      <c r="W277" s="8">
         <v>66.5</v>
       </c>
-      <c r="X277" s="104">
+      <c r="X277" s="39">
         <v>8.3000000000000007</v>
       </c>
-      <c r="Y277" s="104">
+      <c r="Y277" s="39">
         <v>75.2</v>
       </c>
-      <c r="Z277" s="95">
-        <v>200</v>
-      </c>
-      <c r="AA277" s="95">
+      <c r="Z277" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA277" s="8">
         <v>104.6</v>
       </c>
-      <c r="AB277" s="95">
-        <v>2.0999999999999999E-3</v>
-      </c>
-      <c r="AC277" s="95">
+      <c r="AB277" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC277" s="8">
         <v>0.99739999999999995</v>
       </c>
       <c r="AD277" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="AE277" s="95">
+      <c r="AE277" s="8">
         <v>1016</v>
       </c>
-      <c r="AF277" s="118"/>
+      <c r="AF277" s="103"/>
       <c r="AG277" s="52"/>
       <c r="AH277" s="3">
         <v>2.0960000000000001</v>
@@ -26499,10 +26491,10 @@
       <c r="AD278" s="27">
         <v>23.9</v>
       </c>
-      <c r="AE278" s="111">
+      <c r="AE278" s="27">
         <v>1016</v>
       </c>
-      <c r="AF278" s="118"/>
+      <c r="AF278" s="103"/>
       <c r="AG278" s="60"/>
       <c r="AH278" s="3">
         <v>0</v>
@@ -26573,10 +26565,10 @@
       <c r="AD279" s="27">
         <v>23.9</v>
       </c>
-      <c r="AE279" s="111">
+      <c r="AE279" s="27">
         <v>1016</v>
       </c>
-      <c r="AF279" s="118"/>
+      <c r="AF279" s="103"/>
       <c r="AG279" s="52"/>
       <c r="AH279" s="3">
         <v>2.0960000000000001</v>
@@ -26649,11 +26641,11 @@
       <c r="AD280" s="27">
         <v>23.9</v>
       </c>
-      <c r="AE280" s="111">
+      <c r="AE280" s="27">
         <v>1016</v>
       </c>
       <c r="AF280" s="83"/>
-      <c r="AG280" s="95"/>
+      <c r="AG280" s="8"/>
       <c r="AH280" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -26727,11 +26719,11 @@
       <c r="AD281" s="27">
         <v>24.3</v>
       </c>
-      <c r="AE281" s="111">
+      <c r="AE281" s="27">
         <v>1016</v>
       </c>
       <c r="AF281" s="83"/>
-      <c r="AG281" s="95"/>
+      <c r="AG281" s="8"/>
       <c r="AH281" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -26805,11 +26797,11 @@
       <c r="AD282" s="27">
         <v>24.3</v>
       </c>
-      <c r="AE282" s="111">
+      <c r="AE282" s="27">
         <v>1016</v>
       </c>
       <c r="AF282" s="83"/>
-      <c r="AG282" s="95"/>
+      <c r="AG282" s="8"/>
       <c r="AH282" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -26883,11 +26875,11 @@
       <c r="AD283" s="27">
         <v>24.3</v>
       </c>
-      <c r="AE283" s="111">
+      <c r="AE283" s="27">
         <v>1016</v>
       </c>
       <c r="AF283" s="83"/>
-      <c r="AG283" s="95"/>
+      <c r="AG283" s="8"/>
       <c r="AH283" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -26969,11 +26961,11 @@
       <c r="AD284" s="16">
         <v>26.9</v>
       </c>
-      <c r="AE284" s="115">
+      <c r="AE284" s="16">
         <v>1009</v>
       </c>
       <c r="AF284" s="83"/>
-      <c r="AG284" s="115">
+      <c r="AG284" s="16">
         <v>1.1639999999999999</v>
       </c>
       <c r="AH284" s="3">
@@ -27053,11 +27045,11 @@
       <c r="AD285" s="16">
         <v>26.9</v>
       </c>
-      <c r="AE285" s="115">
+      <c r="AE285" s="16">
         <v>1009</v>
       </c>
       <c r="AF285" s="83"/>
-      <c r="AG285" s="115">
+      <c r="AG285" s="16">
         <v>1.1639999999999999</v>
       </c>
       <c r="AH285" s="3">
@@ -27373,9 +27365,9 @@
       <c r="X289" s="62">
         <v>8</v>
       </c>
-      <c r="Y289" s="62" t="e">
+      <c r="Y289" s="62">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>0</v>
       </c>
       <c r="Z289" s="62">
         <v>200</v>
@@ -27462,7 +27454,7 @@
       </c>
       <c r="Y290" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z290" s="62">
         <v>200</v>
@@ -27513,8 +27505,8 @@
       <c r="J291" s="85">
         <v>0.1837</v>
       </c>
-      <c r="K291" s="97"/>
-      <c r="L291" s="97"/>
+      <c r="K291" s="10"/>
+      <c r="L291" s="10"/>
       <c r="M291" s="10"/>
       <c r="N291" s="10"/>
       <c r="O291" s="17"/>
@@ -27547,7 +27539,7 @@
       </c>
       <c r="Y291" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z291" s="62">
         <v>200</v>
@@ -27598,8 +27590,8 @@
       <c r="J292" s="85">
         <v>0.18260000000000001</v>
       </c>
-      <c r="K292" s="97"/>
-      <c r="L292" s="97"/>
+      <c r="K292" s="10"/>
+      <c r="L292" s="10"/>
       <c r="M292" s="10"/>
       <c r="N292" s="10"/>
       <c r="O292" s="17"/>
@@ -27632,7 +27624,7 @@
       </c>
       <c r="Y292" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z292" s="62">
         <v>200</v>
@@ -27653,7 +27645,7 @@
         <v>999.3</v>
       </c>
       <c r="AF292" s="83"/>
-      <c r="AG292" s="107"/>
+      <c r="AG292" s="97"/>
       <c r="AH292" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -27717,7 +27709,7 @@
       </c>
       <c r="Y293" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z293" s="62">
         <v>200</v>
@@ -27738,7 +27730,7 @@
         <v>999.4</v>
       </c>
       <c r="AF293" s="83"/>
-      <c r="AG293" s="107"/>
+      <c r="AG293" s="97"/>
       <c r="AH293" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -27788,7 +27780,7 @@
       </c>
       <c r="Y294" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z294" s="62">
         <v>200</v>
@@ -27809,7 +27801,7 @@
         <v>998</v>
       </c>
       <c r="AF294" s="83"/>
-      <c r="AG294" s="107"/>
+      <c r="AG294" s="97"/>
       <c r="AH294" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -27859,7 +27851,7 @@
       </c>
       <c r="Y295" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z295" s="8">
         <v>200</v>
@@ -27878,7 +27870,7 @@
         <v>999</v>
       </c>
       <c r="AF295" s="83"/>
-      <c r="AG295" s="107"/>
+      <c r="AG295" s="97"/>
       <c r="AH295" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -27928,7 +27920,7 @@
       </c>
       <c r="Y296" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z296" s="8">
         <v>200</v>
@@ -27943,11 +27935,11 @@
       <c r="AD296" s="85">
         <v>25.1</v>
       </c>
-      <c r="AE296" s="116">
+      <c r="AE296" s="85">
         <v>999</v>
       </c>
       <c r="AF296" s="83"/>
-      <c r="AG296" s="107"/>
+      <c r="AG296" s="97"/>
       <c r="AH296" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -27997,7 +27989,7 @@
       </c>
       <c r="Y297" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z297" s="8">
         <v>200</v>
@@ -28012,11 +28004,11 @@
       <c r="AD297" s="85">
         <v>25.3</v>
       </c>
-      <c r="AE297" s="116">
+      <c r="AE297" s="85">
         <v>999</v>
       </c>
       <c r="AF297" s="83"/>
-      <c r="AG297" s="107"/>
+      <c r="AG297" s="97"/>
       <c r="AH297" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28066,7 +28058,7 @@
       </c>
       <c r="Y298" s="62" t="e">
         <f>[1]!Track_TT23[[#This Row],[Rider weight ]]+[1]!Track_TT23[[#This Row],[Bike weight ]]</f>
-        <v>#REF!</v>
+        <v>#VALUE!</v>
       </c>
       <c r="Z298" s="8">
         <v>200</v>
@@ -28081,11 +28073,11 @@
       <c r="AD298" s="85">
         <v>25.2</v>
       </c>
-      <c r="AE298" s="116">
+      <c r="AE298" s="85">
         <v>999</v>
       </c>
       <c r="AF298" s="83"/>
-      <c r="AG298" s="107"/>
+      <c r="AG298" s="97"/>
       <c r="AH298" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28161,9 +28153,9 @@
         <v>99.74</v>
       </c>
       <c r="AD299" s="33"/>
-      <c r="AE299" s="107"/>
+      <c r="AE299" s="97"/>
       <c r="AF299" s="92"/>
-      <c r="AG299" s="95"/>
+      <c r="AG299" s="8"/>
       <c r="AH299" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28241,11 +28233,11 @@
       <c r="AD300" s="85">
         <v>25.4</v>
       </c>
-      <c r="AE300" s="116">
+      <c r="AE300" s="85">
         <v>1003</v>
       </c>
       <c r="AF300" s="92"/>
-      <c r="AG300" s="95"/>
+      <c r="AG300" s="8"/>
       <c r="AH300" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28327,7 +28319,7 @@
         <v>1003</v>
       </c>
       <c r="AF301" s="92"/>
-      <c r="AG301" s="95"/>
+      <c r="AG301" s="8"/>
       <c r="AH301" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28409,7 +28401,7 @@
         <v>1003</v>
       </c>
       <c r="AF302" s="92"/>
-      <c r="AG302" s="95"/>
+      <c r="AG302" s="8"/>
       <c r="AH302" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28491,7 +28483,7 @@
         <v>1003</v>
       </c>
       <c r="AF303" s="92"/>
-      <c r="AG303" s="95"/>
+      <c r="AG303" s="8"/>
       <c r="AH303" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28571,7 +28563,7 @@
         <v>1003</v>
       </c>
       <c r="AF304" s="83"/>
-      <c r="AG304" s="107"/>
+      <c r="AG304" s="97"/>
       <c r="AH304" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28653,7 +28645,7 @@
         <v>1003</v>
       </c>
       <c r="AF305" s="83"/>
-      <c r="AG305" s="107"/>
+      <c r="AG305" s="97"/>
       <c r="AH305" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28735,7 +28727,7 @@
         <v>1003</v>
       </c>
       <c r="AF306" s="83"/>
-      <c r="AG306" s="107"/>
+      <c r="AG306" s="97"/>
       <c r="AH306" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28817,7 +28809,7 @@
         <v>1003</v>
       </c>
       <c r="AF307" s="83"/>
-      <c r="AG307" s="107"/>
+      <c r="AG307" s="97"/>
       <c r="AH307" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28899,7 +28891,7 @@
         <v>1003</v>
       </c>
       <c r="AF308" s="83"/>
-      <c r="AG308" s="107"/>
+      <c r="AG308" s="97"/>
       <c r="AH308" s="3">
         <v>2.0960000000000001</v>
       </c>
@@ -28977,12 +28969,356 @@
       <c r="AD309" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="AE309" s="107">
+      <c r="AE309" s="97">
         <v>1003</v>
       </c>
       <c r="AF309" s="83"/>
-      <c r="AG309" s="107"/>
+      <c r="AG309" s="97"/>
       <c r="AH309" s="3">
+        <v>2.0960000000000001</v>
+      </c>
+    </row>
+    <row r="310" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A310" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C310" s="4">
+        <v>45166</v>
+      </c>
+      <c r="D310" s="105">
+        <v>1</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G310" s="105"/>
+      <c r="H310" s="105"/>
+      <c r="I310" s="26">
+        <v>0.189</v>
+      </c>
+      <c r="J310" s="22">
+        <v>0.1857</v>
+      </c>
+      <c r="K310" s="105"/>
+      <c r="L310" s="105"/>
+      <c r="M310" s="105"/>
+      <c r="N310" s="105"/>
+      <c r="O310" s="23"/>
+      <c r="P310" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q310" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="R310" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="S310" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="T310" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="U310" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="V310" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="W310" s="5"/>
+      <c r="X310" s="3"/>
+      <c r="Y310" s="8">
+        <v>82.5</v>
+      </c>
+      <c r="Z310" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA310" s="8">
+        <v>104</v>
+      </c>
+      <c r="AB310" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC310" s="8">
+        <v>99.74</v>
+      </c>
+      <c r="AD310" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE310" s="69">
+        <v>1012</v>
+      </c>
+      <c r="AF310" s="97">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AG310" s="97">
+        <v>1.18</v>
+      </c>
+      <c r="AH310" s="8">
+        <v>2.0960000000000001</v>
+      </c>
+    </row>
+    <row r="311" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A311" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C311" s="4">
+        <v>45166</v>
+      </c>
+      <c r="D311" s="105">
+        <v>2</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="G311" s="105"/>
+      <c r="H311" s="105"/>
+      <c r="I311" s="26">
+        <v>0.187</v>
+      </c>
+      <c r="J311" s="22">
+        <v>0.18440000000000001</v>
+      </c>
+      <c r="K311" s="105"/>
+      <c r="L311" s="105"/>
+      <c r="M311" s="105"/>
+      <c r="N311" s="105"/>
+      <c r="O311" s="23"/>
+      <c r="P311" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q311" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="R311" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="S311" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="T311" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="U311" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="V311" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="W311" s="5"/>
+      <c r="X311" s="3"/>
+      <c r="Y311" s="8">
+        <v>82.5</v>
+      </c>
+      <c r="Z311" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA311" s="8">
+        <v>104</v>
+      </c>
+      <c r="AB311" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC311" s="8">
+        <v>99.74</v>
+      </c>
+      <c r="AD311" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE311" s="69">
+        <v>1012</v>
+      </c>
+      <c r="AF311" s="97">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AG311" s="97">
+        <v>1.18</v>
+      </c>
+      <c r="AH311" s="8">
+        <v>2.0960000000000001</v>
+      </c>
+    </row>
+    <row r="312" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A312" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="C312" s="4">
+        <v>45166</v>
+      </c>
+      <c r="D312" s="105">
+        <v>3</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="G312" s="105"/>
+      <c r="H312" s="105"/>
+      <c r="I312" s="26">
+        <v>0.182</v>
+      </c>
+      <c r="J312" s="22">
+        <v>0.18129999999999999</v>
+      </c>
+      <c r="K312" s="105"/>
+      <c r="L312" s="105"/>
+      <c r="M312" s="105"/>
+      <c r="N312" s="105"/>
+      <c r="O312" s="23"/>
+      <c r="P312" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q312" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="R312" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="S312" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="T312" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="U312" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="V312" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="W312" s="5"/>
+      <c r="X312" s="3"/>
+      <c r="Y312" s="8">
+        <v>82.5</v>
+      </c>
+      <c r="Z312" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA312" s="8">
+        <v>104</v>
+      </c>
+      <c r="AB312" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC312" s="8">
+        <v>99.74</v>
+      </c>
+      <c r="AD312" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE312" s="69">
+        <v>1012</v>
+      </c>
+      <c r="AF312" s="97">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AG312" s="97">
+        <v>1.18</v>
+      </c>
+      <c r="AH312" s="8">
+        <v>2.0960000000000001</v>
+      </c>
+    </row>
+    <row r="313" spans="1:34" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A313" s="106" t="s">
+        <v>303</v>
+      </c>
+      <c r="B313" s="106" t="s">
+        <v>408</v>
+      </c>
+      <c r="C313" s="107">
+        <v>45166</v>
+      </c>
+      <c r="D313" s="108">
+        <v>4</v>
+      </c>
+      <c r="E313" s="107" t="s">
+        <v>409</v>
+      </c>
+      <c r="F313" s="107" t="s">
+        <v>416</v>
+      </c>
+      <c r="G313" s="108"/>
+      <c r="H313" s="108"/>
+      <c r="I313" s="26">
+        <v>0.182</v>
+      </c>
+      <c r="J313" s="22">
+        <v>0.18310000000000001</v>
+      </c>
+      <c r="K313" s="108"/>
+      <c r="L313" s="108"/>
+      <c r="M313" s="108"/>
+      <c r="N313" s="108"/>
+      <c r="O313" s="109"/>
+      <c r="P313" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q313" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="R313" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="S313" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="T313" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="U313" s="8" t="s">
+        <v>358</v>
+      </c>
+      <c r="V313" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="W313" s="110"/>
+      <c r="X313" s="106"/>
+      <c r="Y313" s="8">
+        <v>82.5</v>
+      </c>
+      <c r="Z313" s="8">
+        <v>200</v>
+      </c>
+      <c r="AA313" s="8">
+        <v>104</v>
+      </c>
+      <c r="AB313" s="8">
+        <v>2.0999999999999999E-3</v>
+      </c>
+      <c r="AC313" s="8">
+        <v>99.74</v>
+      </c>
+      <c r="AD313" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="AE313" s="69">
+        <v>1012</v>
+      </c>
+      <c r="AF313" s="97">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="AG313" s="97">
+        <v>1.18</v>
+      </c>
+      <c r="AH313" s="8">
         <v>2.0960000000000001</v>
       </c>
     </row>
@@ -29040,13 +29376,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -29298,27 +29633,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Campaign xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Year xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+    <Squad xmlns="65551c38-962b-4cee-924d-ef2df1bb8b98" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -29343,9 +29670,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2AA00597-2AFA-4BE4-9EEA-BCD198E427CB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12E8B3F5-660B-4A23-B643-F4910670CCFF}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="65551c38-962b-4cee-924d-ef2df1bb8b98"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="ec750ee3-7d64-422f-9b1f-0ca7238893a8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>